--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/SOUTH_DAKOTA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/SOUTH_DAKOTA_2023.xlsx
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C62">
